--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.43320081217416</v>
+        <v>6.082895131978302</v>
       </c>
       <c r="D2" t="n">
-        <v>38.22395440569058</v>
+        <v>6.211392590924719</v>
       </c>
       <c r="E2" t="n">
-        <v>10.37758881178232</v>
+        <v>1.686358181914628</v>
       </c>
       <c r="F2" t="n">
-        <v>10.33432615756182</v>
+        <v>1.679328000603796</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.15524877085788</v>
+        <v>7.012727925264405</v>
       </c>
       <c r="D3" t="n">
-        <v>43.42328219586914</v>
+        <v>7.056283356828736</v>
       </c>
       <c r="E3" t="n">
-        <v>10.37758881178232</v>
+        <v>1.686358181914628</v>
       </c>
       <c r="F3" t="n">
-        <v>10.33432615756182</v>
+        <v>1.679328000603796</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.64338250755169</v>
+        <v>6.92954965747715</v>
       </c>
       <c r="D4" t="n">
-        <v>42.55606642076742</v>
+        <v>6.915360793374705</v>
       </c>
       <c r="E4" t="n">
-        <v>10.37758881178232</v>
+        <v>1.686358181914628</v>
       </c>
       <c r="F4" t="n">
-        <v>10.33432615756182</v>
+        <v>1.679328000603796</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.1601808783608</v>
+        <v>6.038529392733631</v>
       </c>
       <c r="D5" t="n">
-        <v>37.29896482818027</v>
+        <v>6.061081784579294</v>
       </c>
       <c r="E5" t="n">
-        <v>10.37758881178232</v>
+        <v>1.686358181914628</v>
       </c>
       <c r="F5" t="n">
-        <v>10.33432615756182</v>
+        <v>1.679328000603796</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.75152644268813</v>
+        <v>6.459623046936821</v>
       </c>
       <c r="D6" t="n">
-        <v>37.25130163571398</v>
+        <v>6.053336515803522</v>
       </c>
       <c r="E6" t="n">
-        <v>10.37758881178232</v>
+        <v>1.686358181914628</v>
       </c>
       <c r="F6" t="n">
-        <v>10.33432615756182</v>
+        <v>1.679328000603796</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.23219750405169</v>
+        <v>7.8377320944084</v>
       </c>
       <c r="D7" t="n">
-        <v>48.02637861885638</v>
+        <v>7.804286525564163</v>
       </c>
       <c r="E7" t="n">
-        <v>10.37758881178232</v>
+        <v>1.686358181914628</v>
       </c>
       <c r="F7" t="n">
-        <v>10.33432615756182</v>
+        <v>1.679328000603796</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.20937746113616</v>
+        <v>2.146523837434626</v>
       </c>
       <c r="D8" t="n">
-        <v>13.41132574038028</v>
+        <v>2.179340432811796</v>
       </c>
       <c r="E8" t="n">
-        <v>10.37758881178232</v>
+        <v>1.686358181914628</v>
       </c>
       <c r="F8" t="n">
-        <v>10.33432615756182</v>
+        <v>1.679328000603796</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.52051473086851</v>
+        <v>5.609583643766133</v>
       </c>
       <c r="D9" t="n">
-        <v>34.40224096257506</v>
+        <v>5.590364156418448</v>
       </c>
       <c r="E9" t="n">
-        <v>10.37758881178232</v>
+        <v>1.686358181914628</v>
       </c>
       <c r="F9" t="n">
-        <v>10.33432615756182</v>
+        <v>1.679328000603796</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.54123970063107</v>
+        <v>7.88795145135255</v>
       </c>
       <c r="D10" t="n">
-        <v>48.77215426283634</v>
+        <v>7.925475067710905</v>
       </c>
       <c r="E10" t="n">
-        <v>10.37758881178232</v>
+        <v>1.686358181914628</v>
       </c>
       <c r="F10" t="n">
-        <v>10.33432615756182</v>
+        <v>1.679328000603796</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.55330616094989</v>
+        <v>8.539912251154359</v>
       </c>
       <c r="D11" t="n">
-        <v>52.40360114247994</v>
+        <v>8.515585185652991</v>
       </c>
       <c r="E11" t="n">
-        <v>10.37758881178232</v>
+        <v>1.686358181914628</v>
       </c>
       <c r="F11" t="n">
-        <v>10.33432615756182</v>
+        <v>1.679328000603796</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
